--- a/data/trans_orig/P6907S1-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P6907S1-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>3608</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5488</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6393</t>
+          <t>7112</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>41735</t>
+          <t>42564</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,39%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>59638</t>
+          <t>58919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12993</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>32386</t>
+          <t>33848</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5955</t>
+          <t>6116</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>19054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23523</t>
+          <t>23071</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46993</t>
+          <t>46765</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109905</t>
+          <t>108443</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>129298</t>
+          <t>128351</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>61193</t>
+          <t>60221</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>73320</t>
+          <t>73159</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>174573</t>
+          <t>174801</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>198043</t>
+          <t>198495</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,79%</t>
+          <t>78,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4494</t>
+          <t>4489</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2245</t>
+          <t>2655</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12385</t>
+          <t>12656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8345</t>
+          <t>8598</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23188</t>
+          <t>23875</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,18%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110515</t>
+          <t>110663</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>121534</t>
+          <t>121539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>57657</t>
+          <t>57386</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67797</t>
+          <t>67387</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,32%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>172882</t>
+          <t>172195</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187725</t>
+          <t>187472</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>3796</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>15511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1016</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9320</t>
+          <t>9715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7137</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>22029</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,87%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94914</t>
+          <t>95599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>107193</t>
+          <t>107314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>27717</t>
+          <t>27322</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35959</t>
+          <t>36021</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,83%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>126374</t>
+          <t>126118</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>140990</t>
+          <t>141010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,18%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>953</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4996</t>
+          <t>4943</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1859</t>
+          <t>1894</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>37544</t>
+          <t>36813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44936</t>
+          <t>44929</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8913</t>
+          <t>8966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>49252</t>
+          <t>49033</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57932</t>
+          <t>57897</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,83%</t>
         </is>
       </c>
     </row>
@@ -2791,97 +2791,97 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>633</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2904,97 +2904,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
           <t>821</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>22,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>821</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>31374</t>
+          <t>32292</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>57283</t>
+          <t>57892</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16145</t>
+          <t>15931</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34298</t>
+          <t>35361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>52223</t>
+          <t>52127</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>84638</t>
+          <t>84594</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>415022</t>
+          <t>414413</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>440931</t>
+          <t>440013</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>185823</t>
+          <t>184760</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>203976</t>
+          <t>204190</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,42%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,76%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>607789</t>
+          <t>607833</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>640204</t>
+          <t>640300</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2012 (tasa de respuesta: 44,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,97 +3712,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>954</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1330</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>44,41%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1534</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1666</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2996</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>4233</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>816</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6986</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4961</t>
+          <t>4005</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>931</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8389</t>
+          <t>9114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>13,31%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32081</t>
+          <t>31631</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>37786</t>
+          <t>37801</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>81,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24913</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>60102</t>
+          <t>59377</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>67546</t>
+          <t>67560</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,64%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1052</t>
+          <t>1019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8659</t>
+          <t>9259</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>6389</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2034</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12039</t>
+          <t>11701</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>13,46%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35112</t>
+          <t>34512</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>42719</t>
+          <t>42752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>78,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37054</t>
+          <t>36785</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4561,7 +4561,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74906</t>
+          <t>75244</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>84911</t>
+          <t>84924</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,15%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -4741,97 +4741,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>1974</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>1859</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>13,49%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1990</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36272</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38246</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11926</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13785</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>50041</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52031</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4708</t>
+          <t>4473</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,62 +5119,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1764</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5079</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>17,08%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>4093</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>3,25%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>16,36%</t>
         </is>
       </c>
     </row>
@@ -5197,7 +5197,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15999</t>
+          <t>16234</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>78,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8568</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10332</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,7 +5267,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26946</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>83,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3828</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13864</t>
+          <t>15108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>901</t>
+          <t>865</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7739</t>
+          <t>7292</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5467</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18377</t>
+          <t>18786</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>128713</t>
+          <t>127469</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>138749</t>
+          <t>138869</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>92422</t>
+          <t>92869</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99260</t>
+          <t>99296</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>224361</t>
+          <t>223952</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>237048</t>
+          <t>237271</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>4333</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,62 +6726,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1007</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1689</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5360</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>3,5%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1007</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6883</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>18,61%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11992</t>
+          <t>12818</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21911</t>
+          <t>23434</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,09%</t>
+          <t>81,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10020</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7979</t>
+          <t>8297</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7089,7 +7089,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2685</t>
+          <t>2759</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12944</t>
+          <t>13192</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>71552</t>
+          <t>71385</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>80559</t>
+          <t>80562</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,7 +7162,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>38312</t>
+          <t>37994</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -7197,7 +7197,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>114919</t>
+          <t>114671</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>125178</t>
+          <t>125104</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,84%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8804</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7417,7 +7417,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4185</t>
+          <t>4391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7432,7 +7432,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10541</t>
+          <t>9558</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7467,7 +7467,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,18%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>104319</t>
+          <t>103617</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>112181</t>
+          <t>112193</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,7 +7525,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67273</t>
+          <t>67067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>174040</t>
+          <t>175023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>182836</t>
+          <t>182822</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,7 +7575,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1083</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8855</t>
+          <t>8970</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7760,7 +7760,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5316</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7775,7 +7775,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10972</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82573</t>
+          <t>82458</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>90345</t>
+          <t>90352</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7868,7 +7868,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>50791</t>
+          <t>50762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -7883,7 +7883,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>136563</t>
+          <t>136526</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>146415</t>
+          <t>146429</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -8063,97 +8063,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1095</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5314</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,66%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>17,25%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>1095</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>5475</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,55%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5568</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>17,78%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1095</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5618</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42758</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>44848</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,7 +8211,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25324</t>
+          <t>25485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70028</t>
+          <t>70078</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -8406,97 +8406,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>56,93%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8519,97 +8519,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>810</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
           <t>1880</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>43,07%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>810</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>1880</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21090</t>
+          <t>20359</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11770</t>
+          <t>12838</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10744</t>
+          <t>10465</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>26956</t>
+          <t>29009</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>328911</t>
+          <t>329642</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>343179</t>
+          <t>343846</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>204528</t>
+          <t>203460</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>214425</t>
+          <t>214384</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>539343</t>
+          <t>537290</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>555555</t>
+          <t>555834</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,15%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023</t>
+          <t>Población según si su trabajo le afecta de manera que tiene algún otro problema en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,97 +9670,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2688</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8806</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>36,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>57,39%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2688</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>9745</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>17,52%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>10846</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>12,6%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>63,51%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2688</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>11102</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>12,6%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>50,84%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5989</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,7 +9818,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>6538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -9833,7 +9833,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>42,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -9853,7 +9853,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10231</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -9868,7 +9868,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>482</t>
+          <t>354</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2096</t>
+          <t>1992</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12372</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4434</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21005</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>42355</t>
+          <t>40801</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58592</t>
+          <t>58720</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>37577</t>
+          <t>37479</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>47853</t>
+          <t>47957</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>88017</t>
+          <t>86995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>104359</t>
+          <t>104588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7392</t>
+          <t>7759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22369</t>
+          <t>22515</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3434</t>
+          <t>3213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13404</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29989</t>
+          <t>29505</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73162</t>
+          <t>73016</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88139</t>
+          <t>87772</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63737</t>
+          <t>63615</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72118</t>
+          <t>72339</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>141095</t>
+          <t>141579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>157680</t>
+          <t>156912</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>82,47%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,72%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3593</t>
+          <t>4163</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16764</t>
+          <t>15979</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3465</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13793</t>
+          <t>14045</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27628</t>
+          <t>27695</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,51%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>91789</t>
+          <t>92574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>104960</t>
+          <t>104390</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141156</t>
+          <t>140904</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>151484</t>
+          <t>151573</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235874</t>
+          <t>235807</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253756</t>
+          <t>253531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4818</t>
+          <t>4742</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14680</t>
+          <t>15634</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9689</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9305</t>
+          <t>9110</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22215</t>
+          <t>21430</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52756</t>
+          <t>51802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>62618</t>
+          <t>62694</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>76,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45535</t>
+          <t>45818</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52912</t>
+          <t>52730</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>100728</t>
+          <t>101513</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113638</t>
+          <t>113833</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>81,93%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -11385,97 +11385,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>894</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,57%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2923</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5836</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>26360</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51294</t>
+          <t>51777</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,12 +12086,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>19193</t>
+          <t>19415</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>41055</t>
+          <t>41707</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>49477</t>
+          <t>50220</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83611</t>
+          <t>84552</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>288211</t>
+          <t>287728</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>312746</t>
+          <t>313145</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12199,12 +12199,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>84,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>313160</t>
+          <t>312508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>335022</t>
+          <t>334800</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>610109</t>
+          <t>609168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>644243</t>
+          <t>643500</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,76%</t>
         </is>
       </c>
     </row>
